--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K416"/>
+  <dimension ref="A1:K419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16660,6 +16660,123 @@
         <v>383.89</v>
       </c>
       <c r="K416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>360.51</v>
+      </c>
+      <c r="C417" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="D417" t="n">
+        <v>377.61</v>
+      </c>
+      <c r="E417" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="F417" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="G417" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="H417" t="n">
+        <v>379.73</v>
+      </c>
+      <c r="I417" t="n">
+        <v>378.02</v>
+      </c>
+      <c r="J417" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="C418" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="D418" t="n">
+        <v>378.25</v>
+      </c>
+      <c r="E418" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="F418" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="G418" t="n">
+        <v>381.83</v>
+      </c>
+      <c r="H418" t="n">
+        <v>379.65</v>
+      </c>
+      <c r="I418" t="n">
+        <v>378.49</v>
+      </c>
+      <c r="J418" t="n">
+        <v>383.73</v>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="C419" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="D419" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="E419" t="n">
+        <v>370.69</v>
+      </c>
+      <c r="F419" t="n">
+        <v>383</v>
+      </c>
+      <c r="G419" t="n">
+        <v>382.13</v>
+      </c>
+      <c r="H419" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="I419" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="J419" t="n">
+        <v>383.73</v>
+      </c>
+      <c r="K419" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16676,7 +16793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B436"/>
+  <dimension ref="A1:B439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21039,6 +21156,36 @@
       </c>
       <c r="B436" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -21207,28 +21354,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03605744412056544</v>
+        <v>-0.03810603753271097</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005704856591120522</v>
+        <v>0.006462850381192431</v>
       </c>
       <c r="M2" t="n">
-        <v>2.808862077439022</v>
+        <v>2.798408775155639</v>
       </c>
       <c r="N2" t="n">
-        <v>12.32309224830383</v>
+        <v>12.24843672031953</v>
       </c>
       <c r="O2" t="n">
-        <v>3.510426220319098</v>
+        <v>3.499776667205999</v>
       </c>
       <c r="P2" t="n">
-        <v>362.7712299245337</v>
+        <v>362.793141665959</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21285,28 +21432,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05526866376755608</v>
+        <v>-0.05590171710278719</v>
       </c>
       <c r="J3" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02827076596539035</v>
+        <v>0.02935078333746466</v>
       </c>
       <c r="M3" t="n">
-        <v>1.900203208907842</v>
+        <v>1.889813849089797</v>
       </c>
       <c r="N3" t="n">
-        <v>5.709852077322385</v>
+        <v>5.670560395586174</v>
       </c>
       <c r="O3" t="n">
-        <v>2.389529677012274</v>
+        <v>2.381293849063188</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1625297517975</v>
+        <v>369.1692954471048</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21363,28 +21510,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04404942798948221</v>
+        <v>-0.04321367136495727</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02445692584042813</v>
+        <v>0.02391722321216783</v>
       </c>
       <c r="M4" t="n">
-        <v>1.520433560310403</v>
+        <v>1.513919179946347</v>
       </c>
       <c r="N4" t="n">
-        <v>4.19258160348018</v>
+        <v>4.165593206691385</v>
       </c>
       <c r="O4" t="n">
-        <v>2.047579449857851</v>
+        <v>2.040978492461737</v>
       </c>
       <c r="P4" t="n">
-        <v>378.662491562854</v>
+        <v>378.6535395080958</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21441,28 +21588,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01221749451788941</v>
+        <v>0.009721062049154853</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008492496857798182</v>
+        <v>0.0005453805918822496</v>
       </c>
       <c r="M5" t="n">
-        <v>2.42205316155985</v>
+        <v>2.418336725577436</v>
       </c>
       <c r="N5" t="n">
-        <v>9.512974318249741</v>
+        <v>9.465628703431699</v>
       </c>
       <c r="O5" t="n">
-        <v>3.084310995708724</v>
+        <v>3.07662618844599</v>
       </c>
       <c r="P5" t="n">
-        <v>372.2075416652398</v>
+        <v>372.2342691817947</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21519,28 +21666,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02099020483708512</v>
+        <v>0.02437754391805268</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002427153249618397</v>
+        <v>0.003311120781987142</v>
       </c>
       <c r="M6" t="n">
-        <v>2.577308600647554</v>
+        <v>2.577044781222853</v>
       </c>
       <c r="N6" t="n">
-        <v>9.80928085387178</v>
+        <v>9.777394044618125</v>
       </c>
       <c r="O6" t="n">
-        <v>3.131977147725025</v>
+        <v>3.126882480141862</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1566959494376</v>
+        <v>380.1204335816374</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21597,28 +21744,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.005062605191594101</v>
+        <v>-0.002736924760332216</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K7" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002666673364406513</v>
+        <v>7.894535116381718e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.773488177022763</v>
+        <v>1.770071973467479</v>
       </c>
       <c r="N7" t="n">
-        <v>5.204977593588985</v>
+        <v>5.185892419247655</v>
       </c>
       <c r="O7" t="n">
-        <v>2.28144199873435</v>
+        <v>2.277255457617273</v>
       </c>
       <c r="P7" t="n">
-        <v>380.446930182196</v>
+        <v>380.4220297043032</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21675,28 +21822,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03991590531577632</v>
+        <v>0.03842920121062375</v>
       </c>
       <c r="J8" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K8" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01840634671560804</v>
+        <v>0.01732997979288142</v>
       </c>
       <c r="M8" t="n">
-        <v>1.727712646055583</v>
+        <v>1.72129596617593</v>
       </c>
       <c r="N8" t="n">
-        <v>4.602698267748548</v>
+        <v>4.577106299557353</v>
       </c>
       <c r="O8" t="n">
-        <v>2.145390003647017</v>
+        <v>2.139417280372708</v>
       </c>
       <c r="P8" t="n">
-        <v>379.6047249480109</v>
+        <v>379.6206423980325</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21753,28 +21900,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06982959460896025</v>
+        <v>0.06808381131510356</v>
       </c>
       <c r="J9" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K9" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05343611641122559</v>
+        <v>0.05160868936953888</v>
       </c>
       <c r="M9" t="n">
-        <v>1.705344293310792</v>
+        <v>1.700728058680378</v>
       </c>
       <c r="N9" t="n">
-        <v>4.678972349651899</v>
+        <v>4.655979815036982</v>
       </c>
       <c r="O9" t="n">
-        <v>2.163093236467605</v>
+        <v>2.157771956217103</v>
       </c>
       <c r="P9" t="n">
-        <v>377.6839701126888</v>
+        <v>377.7026566363139</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21831,28 +21978,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01629894830830918</v>
+        <v>-0.01760490373589523</v>
       </c>
       <c r="J10" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K10" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004584625764576633</v>
+        <v>0.005421483413132422</v>
       </c>
       <c r="M10" t="n">
-        <v>1.448947883598594</v>
+        <v>1.445050467844045</v>
       </c>
       <c r="N10" t="n">
-        <v>3.124467509418903</v>
+        <v>3.107755786464352</v>
       </c>
       <c r="O10" t="n">
-        <v>1.767616335469579</v>
+        <v>1.762882805652251</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0715523872294</v>
+        <v>385.0855335895222</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21890,7 +22037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K416"/>
+  <dimension ref="A1:K419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45589,6 +45736,177 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-36.74563757302753,175.16856437798262</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-36.74633173930397,175.16869813927252</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-36.74701081163913,175.16896564040786</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-36.74769049028625,175.16911446396907</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-36.748321494426776,175.1694595371866</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-36.74891204897178,175.16988078564447</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-36.749483410960586,175.17038232346673</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-36.74999831725438,175.17098348684667</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-36.75046107380346,175.17166979614748</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-36.74563764274814,175.1685633740195</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-36.74633143221439,175.16870091231624</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-36.74700949562132,175.16897261727186</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-36.747690709051795,175.1691134936074</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-36.748322359570544,175.1694570743225</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-36.74891184468657,175.16988115463872</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-36.7494838868218,175.17038165061237</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-36.74999527724229,175.17098715082952</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-36.75046120477228,175.1716696423177</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-36.745637774442585,175.16856147764466</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-36.74633094087093,175.16870534918607</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-36.747009331119074,175.16897348937985</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-36.74769102504642,175.1691120919739</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-36.74832221537993,175.16945748479984</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-36.74891031254743,175.16988392209547</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-36.74948448164833,175.17038080954444</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-36.74999508319897,175.17098738470074</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-36.75046120477228,175.1716696423177</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K419"/>
+  <dimension ref="A1:K421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16777,6 +16777,84 @@
         <v>383.73</v>
       </c>
       <c r="K419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>360.36</v>
+      </c>
+      <c r="C420" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="D420" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="E420" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="F420" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="G420" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="H420" t="n">
+        <v>380.23</v>
+      </c>
+      <c r="I420" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="J420" t="n">
+        <v>383.91</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:27+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="C421" t="n">
+        <v>366.53</v>
+      </c>
+      <c r="D421" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="E421" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="F421" t="n">
+        <v>381.74</v>
+      </c>
+      <c r="G421" t="n">
+        <v>381.53</v>
+      </c>
+      <c r="H421" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="I421" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="J421" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="K421" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16793,7 +16871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B439"/>
+  <dimension ref="A1:B441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21186,6 +21264,26 @@
       </c>
       <c r="B439" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -21354,28 +21452,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03810603753271097</v>
+        <v>-0.04012515999159241</v>
       </c>
       <c r="J2" t="n">
+        <v>420</v>
+      </c>
+      <c r="K2" t="n">
         <v>418</v>
       </c>
-      <c r="K2" t="n">
-        <v>416</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.006462850381192431</v>
+        <v>0.007223102249072633</v>
       </c>
       <c r="M2" t="n">
-        <v>2.798408775155639</v>
+        <v>2.794601494268161</v>
       </c>
       <c r="N2" t="n">
-        <v>12.24843672031953</v>
+        <v>12.21321137044374</v>
       </c>
       <c r="O2" t="n">
-        <v>3.499776667205999</v>
+        <v>3.494740529773811</v>
       </c>
       <c r="P2" t="n">
-        <v>362.793141665959</v>
+        <v>362.8148027178961</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21432,28 +21530,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05590171710278719</v>
+        <v>-0.05607296412772379</v>
       </c>
       <c r="J3" t="n">
+        <v>420</v>
+      </c>
+      <c r="K3" t="n">
         <v>418</v>
       </c>
-      <c r="K3" t="n">
-        <v>416</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02935078333746466</v>
+        <v>0.02980831975840204</v>
       </c>
       <c r="M3" t="n">
-        <v>1.889813849089797</v>
+        <v>1.885425240933572</v>
       </c>
       <c r="N3" t="n">
-        <v>5.670560395586174</v>
+        <v>5.648010533025239</v>
       </c>
       <c r="O3" t="n">
-        <v>2.381293849063188</v>
+        <v>2.376554340431802</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1692954471048</v>
+        <v>369.1711368714306</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21510,28 +21608,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04321367136495727</v>
+        <v>-0.04308082156565486</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02391722321216783</v>
+        <v>0.02401401959212457</v>
       </c>
       <c r="M4" t="n">
-        <v>1.513919179946347</v>
+        <v>1.509333672705401</v>
       </c>
       <c r="N4" t="n">
-        <v>4.165593206691385</v>
+        <v>4.147242404991634</v>
       </c>
       <c r="O4" t="n">
-        <v>2.040978492461737</v>
+        <v>2.036477941199372</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6535395080958</v>
+        <v>378.6521157026851</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21588,28 +21686,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009721062049154853</v>
+        <v>0.007138947118874395</v>
       </c>
       <c r="J5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005453805918822496</v>
+        <v>0.0002960985738204025</v>
       </c>
       <c r="M5" t="n">
-        <v>2.418336725577436</v>
+        <v>2.421297944495693</v>
       </c>
       <c r="N5" t="n">
-        <v>9.465628703431699</v>
+        <v>9.460544861976992</v>
       </c>
       <c r="O5" t="n">
-        <v>3.07662618844599</v>
+        <v>3.075799873525095</v>
       </c>
       <c r="P5" t="n">
-        <v>372.2342691817947</v>
+        <v>372.2619976692467</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21666,28 +21764,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02437754391805268</v>
+        <v>0.02617065012015405</v>
       </c>
       <c r="J6" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K6" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003311120781987142</v>
+        <v>0.003846865214260142</v>
       </c>
       <c r="M6" t="n">
-        <v>2.577044781222853</v>
+        <v>2.574464588819345</v>
       </c>
       <c r="N6" t="n">
-        <v>9.777394044618125</v>
+        <v>9.751263831673711</v>
       </c>
       <c r="O6" t="n">
-        <v>3.126882480141862</v>
+        <v>3.122701367674102</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1204335816374</v>
+        <v>380.1011859026853</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21744,28 +21842,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.002736924760332216</v>
+        <v>-0.001059312669454612</v>
       </c>
       <c r="J7" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K7" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L7" t="n">
-        <v>7.894535116381718e-05</v>
+        <v>1.191678697154419e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.770071973467479</v>
+        <v>1.768351780945421</v>
       </c>
       <c r="N7" t="n">
-        <v>5.185892419247655</v>
+        <v>5.177221307646383</v>
       </c>
       <c r="O7" t="n">
-        <v>2.277255457617273</v>
+        <v>2.275350809797554</v>
       </c>
       <c r="P7" t="n">
-        <v>380.4220297043032</v>
+        <v>380.4040204756805</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21822,28 +21920,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03842920121062375</v>
+        <v>0.03772462413050713</v>
       </c>
       <c r="J8" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K8" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01732997979288142</v>
+        <v>0.01687580592623872</v>
       </c>
       <c r="M8" t="n">
-        <v>1.72129596617593</v>
+        <v>1.71597134645367</v>
       </c>
       <c r="N8" t="n">
-        <v>4.577106299557353</v>
+        <v>4.558337240467527</v>
       </c>
       <c r="O8" t="n">
-        <v>2.139417280372708</v>
+        <v>2.135026285661965</v>
       </c>
       <c r="P8" t="n">
-        <v>379.6206423980325</v>
+        <v>379.6282086997228</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21900,28 +21998,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06808381131510356</v>
+        <v>0.06723540147147415</v>
       </c>
       <c r="J9" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K9" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05160868936953888</v>
+        <v>0.05086870743498084</v>
       </c>
       <c r="M9" t="n">
-        <v>1.700728058680378</v>
+        <v>1.69632913057734</v>
       </c>
       <c r="N9" t="n">
-        <v>4.655979815036982</v>
+        <v>4.637504486779561</v>
       </c>
       <c r="O9" t="n">
-        <v>2.157771956217103</v>
+        <v>2.153486588483792</v>
       </c>
       <c r="P9" t="n">
-        <v>377.7026566363139</v>
+        <v>377.7117658007942</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21978,28 +22076,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01760490373589523</v>
+        <v>-0.01820688628190676</v>
       </c>
       <c r="J10" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K10" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005421483413132422</v>
+        <v>0.005854574263434609</v>
       </c>
       <c r="M10" t="n">
-        <v>1.445050467844045</v>
+        <v>1.441133373453422</v>
       </c>
       <c r="N10" t="n">
-        <v>3.107755786464352</v>
+        <v>3.094843601719412</v>
       </c>
       <c r="O10" t="n">
-        <v>1.762882805652251</v>
+        <v>1.759216758025972</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0855335895222</v>
+        <v>385.0919965178497</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22037,7 +22135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K419"/>
+  <dimension ref="A1:K421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45907,6 +46005,120 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-36.74563768922852,175.16856270471072</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-36.746329884481916,175.168714888456</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-36.747009639560794,175.16897185417736</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-36.74769051459354,175.1691143561511</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-36.74832019671103,175.1694632314827</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-36.74890750362551,175.16988899576586</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-36.74948043682786,175.17038652880618</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-36.74999424234455,175.17098839814275</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-36.75046002605274,175.1716710267858</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:27+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-36.745638773770025,175.16854708750606</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-36.74633225521431,175.16869348055909</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-36.74701186034053,175.1689600807192</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-36.74769588650026,175.16909052837948</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-36.748326757383985,175.1694445547623</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-36.748913376825655,175.16987838718185</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-36.74948424371771,175.17038114597162</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-36.74999443638787,175.17098816427153</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-36.75045904378646,175.17167218050912</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0163/nzd0163.xlsx
+++ b/data/nzd0163/nzd0163.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K421"/>
+  <dimension ref="A1:K422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16855,6 +16855,45 @@
         <v>384.06</v>
       </c>
       <c r="K421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>357.06</v>
+      </c>
+      <c r="C422" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="D422" t="n">
+        <v>376.21</v>
+      </c>
+      <c r="E422" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="F422" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="G422" t="n">
+        <v>381.26</v>
+      </c>
+      <c r="H422" t="n">
+        <v>379.27</v>
+      </c>
+      <c r="I422" t="n">
+        <v>378.61</v>
+      </c>
+      <c r="J422" t="n">
+        <v>384.71</v>
+      </c>
+      <c r="K422" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16871,7 +16910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B441"/>
+  <dimension ref="A1:B442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21284,6 +21323,16 @@
       </c>
       <c r="B441" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
@@ -21452,28 +21501,28 @@
         <v>0.1573</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04012515999159241</v>
+        <v>-0.04236435712038256</v>
       </c>
       <c r="J2" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007223102249072633</v>
+        <v>0.008053717289738138</v>
       </c>
       <c r="M2" t="n">
-        <v>2.794601494268161</v>
+        <v>2.7984380478088</v>
       </c>
       <c r="N2" t="n">
-        <v>12.21321137044374</v>
+        <v>12.23598552392109</v>
       </c>
       <c r="O2" t="n">
-        <v>3.494740529773811</v>
+        <v>3.497997359050045</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8148027178961</v>
+        <v>362.8389204497403</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21530,28 +21579,28 @@
         <v>0.1392</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05607296412772379</v>
+        <v>-0.0569507035090454</v>
       </c>
       <c r="J3" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02980831975840204</v>
+        <v>0.03083676422326065</v>
       </c>
       <c r="M3" t="n">
-        <v>1.885425240933572</v>
+        <v>1.885518635146517</v>
       </c>
       <c r="N3" t="n">
-        <v>5.648010533025239</v>
+        <v>5.642508962475788</v>
       </c>
       <c r="O3" t="n">
-        <v>2.376554340431802</v>
+        <v>2.375396590566676</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1711368714306</v>
+        <v>369.1805907434259</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21608,28 +21657,28 @@
         <v>0.1896</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04308082156565486</v>
+        <v>-0.04369391688620877</v>
       </c>
       <c r="J4" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02401401959212457</v>
+        <v>0.02479169772956114</v>
       </c>
       <c r="M4" t="n">
-        <v>1.509333672705401</v>
+        <v>1.508570246060521</v>
       </c>
       <c r="N4" t="n">
-        <v>4.147242404991634</v>
+        <v>4.141261849723159</v>
       </c>
       <c r="O4" t="n">
-        <v>2.036477941199372</v>
+        <v>2.035009053965893</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6521157026851</v>
+        <v>378.6587253355835</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21686,28 +21735,28 @@
         <v>0.1049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007138947118874395</v>
+        <v>0.005117393897309932</v>
       </c>
       <c r="J5" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002960985738204025</v>
+        <v>0.0001523055868448697</v>
       </c>
       <c r="M5" t="n">
-        <v>2.421297944495693</v>
+        <v>2.426936054347096</v>
       </c>
       <c r="N5" t="n">
-        <v>9.460544861976992</v>
+        <v>9.480152471634113</v>
       </c>
       <c r="O5" t="n">
-        <v>3.075799873525095</v>
+        <v>3.078985623810886</v>
       </c>
       <c r="P5" t="n">
-        <v>372.2619976692467</v>
+        <v>372.2837915473452</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21764,28 +21813,28 @@
         <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02617065012015405</v>
+        <v>0.02690667690898385</v>
       </c>
       <c r="J6" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K6" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003846865214260142</v>
+        <v>0.004084746143563689</v>
       </c>
       <c r="M6" t="n">
-        <v>2.574464588819345</v>
+        <v>2.57230818285835</v>
       </c>
       <c r="N6" t="n">
-        <v>9.751263831673711</v>
+        <v>9.733679761599376</v>
       </c>
       <c r="O6" t="n">
-        <v>3.122701367674102</v>
+        <v>3.119884575044304</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1011859026853</v>
+        <v>380.0932509752532</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21842,28 +21891,28 @@
         <v>0.1858</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.001059312669454612</v>
+        <v>-0.0006376340407331199</v>
       </c>
       <c r="J7" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K7" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>1.191678697154419e-05</v>
+        <v>4.339331907909916e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>1.768351780945421</v>
+        <v>1.765843222988112</v>
       </c>
       <c r="N7" t="n">
-        <v>5.177221307646383</v>
+        <v>5.16675475216828</v>
       </c>
       <c r="O7" t="n">
-        <v>2.275350809797554</v>
+        <v>2.273049658975422</v>
       </c>
       <c r="P7" t="n">
-        <v>380.4040204756805</v>
+        <v>380.3994744600065</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21920,28 +21969,28 @@
         <v>0.1404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03772462413050713</v>
+        <v>0.03706635846724408</v>
       </c>
       <c r="J8" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K8" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01687580592623872</v>
+        <v>0.01637159457137671</v>
       </c>
       <c r="M8" t="n">
-        <v>1.71597134645367</v>
+        <v>1.714596716073629</v>
       </c>
       <c r="N8" t="n">
-        <v>4.558337240467527</v>
+        <v>4.55197152874332</v>
       </c>
       <c r="O8" t="n">
-        <v>2.135026285661965</v>
+        <v>2.133534984185476</v>
       </c>
       <c r="P8" t="n">
-        <v>379.6282086997228</v>
+        <v>379.6353053032001</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21998,28 +22047,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06723540147147415</v>
+        <v>0.0668024451388865</v>
       </c>
       <c r="J9" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K9" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05086870743498084</v>
+        <v>0.0504840196216223</v>
       </c>
       <c r="M9" t="n">
-        <v>1.69632913057734</v>
+        <v>1.694210869061777</v>
       </c>
       <c r="N9" t="n">
-        <v>4.637504486779561</v>
+        <v>4.628419161703214</v>
       </c>
       <c r="O9" t="n">
-        <v>2.153486588483792</v>
+        <v>2.151376108843643</v>
       </c>
       <c r="P9" t="n">
-        <v>377.7117658007942</v>
+        <v>377.7164333986757</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22076,28 +22125,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01820688628190676</v>
+        <v>-0.01815499936447884</v>
       </c>
       <c r="J10" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K10" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005854574263434609</v>
+        <v>0.005852388686896304</v>
       </c>
       <c r="M10" t="n">
-        <v>1.441133373453422</v>
+        <v>1.437968965540505</v>
       </c>
       <c r="N10" t="n">
-        <v>3.094843601719412</v>
+        <v>3.087520150530081</v>
       </c>
       <c r="O10" t="n">
-        <v>1.759216758025972</v>
+        <v>1.757134073009251</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0919965178497</v>
+        <v>385.0914371374975</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22135,7 +22184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K421"/>
+  <dimension ref="A1:K422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46119,6 +46168,63 @@
         </is>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-36.74564024564451,175.16852589272744</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-36.74633311506451,175.1686857160365</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-36.74701369042667,175.168950378517</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-36.747697004634105,175.16908556875234</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-36.74832459452509,175.16945071192322</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-36.74891475575077,175.1698758964706</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-36.74948614716256,175.1703784545541</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-36.74999450106898,175.17098808631445</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-36.75045478729906,175.17167717997663</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
